--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／101本</t>
+          <t>3／102本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の98本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の99本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表142件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表143件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全101本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全102本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>98／101本が可能</t>
+          <t>99／102本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（142件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（143件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜145</t>
+          <t>No.1〜146</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>142件</t>
+          <t>143件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。**元の4件を残すか、統合報告書に一本化するかはご判断をお願いします**（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は102件（送付33・条件付き48・内部保管16・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は103件（送付33・条件付き49・内部保管16・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>101本（うち再実行できない3本）</t>
+          <t>102本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>142件／一意142件</t>
+          <t>143件／一意143件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>102件＝送付33＋条件付き48＋内部保管16＋対象外5</t>
+          <t>103件＝送付33＋条件付き49＋内部保管16＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／102本</t>
+          <t>3／103本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の99本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の100本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表143件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表145件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全102本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全103本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>99／102本が可能</t>
+          <t>100／103本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（143件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（145件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜146</t>
+          <t>No.1〜148</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>143件</t>
+          <t>145件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。**元の4件を残すか、統合報告書に一本化するかはご判断をお願いします**（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は103件（送付33・条件付き49・内部保管16・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は104件（送付33・条件付き49・内部保管17・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>102本（うち再実行できない3本）</t>
+          <t>103本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>143件／一意143件</t>
+          <t>145件／一意145件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>103件＝送付33＋条件付き49＋内部保管16＋対象外5</t>
+          <t>104件＝送付33＋条件付き49＋内部保管17＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は843段落137表36図です。</t>
+注3）計画素案は886段落142表36図です。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -2740,7 +2740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3037,10 +3037,35 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>注1）10件のうち算定に関わるものが5件、記述が4件、運用が1件です。
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>認定率の差を「分子に第2号被保険者を含むかの違い」としていた</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>R8.9.16</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.125の起票時の見立て。受領資料を数値で確かめないまま原因を1つに決めていた。令和8年9月16日に逆算して確かめたところ、当方の認定率は分子に第2号被保険者の認定者を含んでおらず、見える化システムの総括表にも要介護認定率の行があって1,943÷9,119で小数第6位まで再現できることが分かった</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.125を「将来推計の参考シートの認定率が総括表の認定率と一致しないこと」に絞って書き直した。**差の原因を1つに決める前に、受領資料の数値で逆算して確かめる**</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>注1）11件のうち算定に関わるものが5件、記述が5件、運用が1件です。
 注2）算定に関わる5件のうち、保険料の算定に影響したのは調整交付金の表示（49,113円）のみで、他は表示・推定値の置き方・定員の集計に関わるものです。
 注3）当方の自己点検が見つけたもの4件、ブランチ内資料の点検によるご指摘3件、受領資料の再送により判明したもの1件です。
 注4）いずれも「手立て」の欄に記した内容をCLAUDE.mdの「陥りやすい誤り」に記録し、同じ誤りを繰り返さない形にしています。</t>
@@ -3049,8 +3074,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3361,7 +3386,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>10件</t>
+          <t>11件</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は886段落142表36図です。</t>
+注3）計画素案は893段落143表36図です。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／103本</t>
+          <t>3／104本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の100本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の101本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表145件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表148件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全103本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全104本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>100／103本が可能</t>
+          <t>101／104本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（145件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（148件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜148</t>
+          <t>No.1〜151</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>145件</t>
+          <t>148件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。**元の4件を残すか、統合報告書に一本化するかはご判断をお願いします**（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は104件（送付33・条件付き49・内部保管17・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は105件（送付33・条件付き50・内部保管17・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>103本（うち再実行できない3本）</t>
+          <t>104本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>145件／一意145件</t>
+          <t>148件／一意148件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>104件＝送付33＋条件付き49＋内部保管17＋対象外5</t>
+          <t>105件＝送付33＋条件付き50＋内部保管17＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は893段落143表36図です。</t>
+注3）計画素案は896段落143表36図です。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／104本</t>
+          <t>3／105本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の101本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の102本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表148件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表150件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全104本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全105本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>101／104本が可能</t>
+          <t>102／105本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（148件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（150件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜151</t>
+          <t>No.1〜153</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>148件</t>
+          <t>150件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。**元の4件を残すか、統合報告書に一本化するかはご判断をお願いします**（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は105件（送付33・条件付き50・内部保管17・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は106件（送付33・条件付き50・内部保管18・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>104本（うち再実行できない3本）</t>
+          <t>105本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>148件／一意148件</t>
+          <t>150件／一意150件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>105件＝送付33＋条件付き50＋内部保管17＋対象外5</t>
+          <t>106件＝送付33＋条件付き50＋内部保管18＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／105本</t>
+          <t>3／106本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の102本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の103本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全105本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全106本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>102／105本が可能</t>
+          <t>103／106本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。**元の4件を残すか、統合報告書に一本化するかはご判断をお願いします**（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は106件（送付33・条件付き50・内部保管18・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は107件（送付33・条件付き50・内部保管19・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>105本（うち再実行できない3本）</t>
+          <t>106本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>106件＝送付33＋条件付き50＋内部保管18＋対象外5</t>
+          <t>107件＝送付33＋条件付き50＋内部保管19＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／106本</t>
+          <t>3／107本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の103本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の104本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全106本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全107本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>103／106本が可能</t>
+          <t>104／107本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。**元の4件を残すか、統合報告書に一本化するかはご判断をお願いします**（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は107件（送付33・条件付き50・内部保管19・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は108件（送付33・条件付き51・内部保管19・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>106本（うち再実行できない3本）</t>
+          <t>107本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>107件＝送付33＋条件付き50＋内部保管19＋対象外5</t>
+          <t>108件＝送付33＋条件付き51＋内部保管19＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／107本</t>
+          <t>3／108本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の104本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の105本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表150件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表151件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全107本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全108本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>104／107本が可能</t>
+          <t>105／108本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（150件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（151件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜153</t>
+          <t>No.1〜154</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>150件</t>
+          <t>151件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。**元の4件を残すか、統合報告書に一本化するかはご判断をお願いします**（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は108件（送付33・条件付き51・内部保管19・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は109件（送付33・条件付き51・内部保管20・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>107本（うち再実行できない3本）</t>
+          <t>108本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>150件／一意150件</t>
+          <t>151件／一意151件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>108件＝送付33＋条件付き51＋内部保管19＋対象外5</t>
+          <t>109件＝送付33＋条件付き51＋内部保管20＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／108本</t>
+          <t>3／109本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の105本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の106本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表151件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表154件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全108本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全109本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>105／108本が可能</t>
+          <t>106／109本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（151件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（154件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>151件</t>
+          <t>154件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。**元の4件を残すか、統合報告書に一本化するかはご判断をお願いします**（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は109件（送付33・条件付き51・内部保管20・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は110件（送付33・条件付き51・内部保管21・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>108本（うち再実行できない3本）</t>
+          <t>109本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>151件／一意151件</t>
+          <t>154件／一意154件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>109件＝送付33＋条件付き51＋内部保管20＋対象外5</t>
+          <t>110件＝送付33＋条件付き51＋内部保管21＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／109本</t>
+          <t>3／111本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の106本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の108本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表154件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表157件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全109本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全111本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>106／109本が可能</t>
+          <t>108／111本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（154件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（157件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜154</t>
+          <t>No.1〜157</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>154件</t>
+          <t>157件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。**元の4件を残すか、統合報告書に一本化するかはご判断をお願いします**（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は110件（送付33・条件付き51・内部保管21・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は112件（送付33・条件付き52・内部保管22・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>109本（うち再実行できない3本）</t>
+          <t>111本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>154件／一意154件</t>
+          <t>157件／一意157件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>110件＝送付33＋条件付き51＋内部保管21＋対象外5</t>
+          <t>112件＝送付33＋条件付き52＋内部保管22＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／111本</t>
+          <t>3／114本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の108本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の111本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表157件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表158件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は896段落143表36図です。</t>
+注3）計画素案は926段落145表36図です。</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全111本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全114本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>108／111本が可能</t>
+          <t>111／114本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（157件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（158件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜157</t>
+          <t>No.1〜158</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>157件</t>
+          <t>158件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。**元の4件を残すか、統合報告書に一本化するかはご判断をお願いします**（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は112件（送付33・条件付き52・内部保管22・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は115件（送付34・条件付き53・内部保管23・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>111本（うち再実行できない3本）</t>
+          <t>114本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>157件／一意157件</t>
+          <t>158件／一意158件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>112件＝送付33＋条件付き52＋内部保管22＋対象外5</t>
+          <t>115件＝送付34＋条件付き53＋内部保管23＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／114本</t>
+          <t>3／115本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の111本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の112本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全114本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全115本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>111／114本が可能</t>
+          <t>112／115本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2182,17 +2182,17 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>広域連合単位 3,083,474,291円</t>
+          <t>広域連合単位 3,213,054,558円</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>4.0％</t>
+          <t>0円</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>令和6・8年度は完全一致。要介護度により1.7〜5.9％と幅がある。確認事項No.87。保険料は保険者単位で算定するため年報を用いる</t>
+          <t>令和8年9月25日の再提供により3か年とも要介護度別まで一致した（確認事項No.87は解決）。従前の表の値3,083,474,291円は同じファイルの明細と一致していなかった</t>
         </is>
       </c>
     </row>
@@ -2718,9 +2718,9 @@
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
-注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。**元の4件を残すか、統合報告書に一本化するかはご判断をお願いします**（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
+注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は115件（送付34・条件付き53・内部保管23・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は116件（送付34・条件付き54・内部保管23・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2793,22 +2793,22 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の割合を7.375％と表示していた</t>
+          <t>令和7年度の給付費の差を抽出条件の違いによるものと整理していた</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>R8.9.11</t>
+          <t>R8.9.25</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>実際の計算は7.3755％で、Eの算定で49,113円の差。ブランチ内資料の点検によるご指摘</t>
+          <t>令和8年8月28日受領分の【大雪】令和7年度のファイルの表の値3,083,474,291円を広域連合の実績として扱い、「町別に按分すると3町とも上回る」「広域連合のファイルだけ伸びが趨勢から外れている」と整理していた。同じファイルの明細を集計すると3町合計と要介護度別まで一致する</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>表示を7.3755％に改めた。表示の桁を落とさず、計算に用いた値をそのまま書く</t>
+          <t>再提供を受けたファイルにより差が解消したことを確かめ、従前の整理を取り下げた。表（ピボット）の値は、同じファイルの明細と突き合わせてから用いる</t>
         </is>
       </c>
     </row>
@@ -2818,22 +2818,22 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>`data_shien_tool.SHISETSU` を「定員」と表記していた</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>R8.9.10</t>
+          <t>調整交付金の割合を7.375％と表示していた</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R8.9.11</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>実際は月平均利用者数。町別データシートの表題が誤っていた</t>
+          <t>実際の計算は7.3755％で、Eの算定で49,113円の差。ブランチ内資料の点検によるご指摘</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>「施設・居住系サービスの月平均利用者数」に改めた。定員と読み違えやすい値4つをCLAUDE.mdに記録した</t>
+          <t>表示を7.3755％に改めた。表示の桁を落とさず、計算に用いた値をそのまま書く</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>令和9年度が介護報酬改定の年に当たらないとしていた</t>
+          <t>`data_shien_tool.SHISETSU` を「定員」と表記していた</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>改定は3年周期（H30・R3・R6）であり令和9年度は改定の年。`build_machi_kaito.py` の記述</t>
+          <t>実際は月平均利用者数。町別データシートの表題が誤っていた</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>修正した。改定率1％あたり月額＋61円を算定し、確認事項No.109として起票した</t>
+          <t>「施設・居住系サービスの月平均利用者数」に改めた。定員と読み違えやすい値4つをCLAUDE.mdに記録した</t>
         </is>
       </c>
     </row>
@@ -2868,22 +2868,22 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>「2か年とも基本推計が実績に近い」としていた</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>R8.9.11</t>
+          <t>令和9年度が介護報酬改定の年に当たらないとしていた</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>R8.9.10</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>令和6年度は包括推計の方が1.00に近い。自己点検が検出した</t>
+          <t>改定は3年周期（H30・R3・R6）であり令和9年度は改定の年。`build_machi_kaito.py` の記述</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>2か年平均の絶対誤差（基本0.61％・包括1.23％）で比べる形に改めた。「2か年とも」と書く前に各年を確かめる</t>
+          <t>修正した。改定率1％あたり月額＋61円を算定し、確認事項No.109として起票した</t>
         </is>
       </c>
     </row>
@@ -2893,22 +2893,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の町別定員が誤っていた</t>
+          <t>「2か年とも基本推計が実績に近い」としていた</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>R8.9.10</t>
+          <t>R8.9.11</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>東川町45人→36人、計108人→99人。第2章第3節6及び第6章第4節4の分布欄</t>
+          <t>令和6年度は包括推計の方が1.00に近い。自己点検が検出した</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>修正した。定員は99人＋［要確認］とし、くるみの郷の定員未確定を明示している</t>
+          <t>2か年平均の絶対誤差（基本0.61％・包括1.23％）で比べる形に改めた。「2か年とも」と書く前に各年を確かめる</t>
         </is>
       </c>
     </row>
@@ -2918,22 +2918,22 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>素案の段落・表・図の数が管理表と合っていなかった</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>R8.9.11</t>
+          <t>認知症対応型共同生活介護の町別定員が誤っていた</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>R8.9.10</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>実物806／130／36に対し管理表667／114／34。固定値で書いていたため更新に追随していなかった</t>
+          <t>東川町45人→36人、計108人→99人。第2章第3節6及び第6章第4節4の分布欄</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>`repo_paths.draft_label()` で実物から数える形に改め、6箇所を置換した。件数・項目数は固定値で書かない</t>
+          <t>修正した。定員は99人＋［要確認］とし、くるみの郷の定員未確定を明示している</t>
         </is>
       </c>
     </row>
@@ -2943,22 +2943,22 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>ビルドスクリプトが出力先を絶対パスで固定していた</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
+          <t>素案の段落・表・図の数が管理表と合っていなかった</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>R8.9.11</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>98本中97本。別ブランチの作業ツリーから実行すると生成物がそこへ落ちる。実際に起きた</t>
+          <t>実物806／130／36に対し管理表667／114／34。固定値で書いていたため更新に追随していなかった</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>`repo_paths.py` を新設し `RP.ROOT`（`__file__` 起点）に統一した。全スクリプトを別ディレクトリから実行して確認した</t>
+          <t>`repo_paths.draft_label()` で実物から数える形に改め、6箇所を置換した。件数・項目数は固定値で書かない</t>
         </is>
       </c>
     </row>
@@ -2968,22 +2968,22 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>受領済みの年報の明細を取り込まないまま推定値を作っていた</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
+          <t>ビルドスクリプトが出力先を絶対パスで固定していた</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>R8.9.11</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>年報（令和7年度・資料No.22）に要介護度別の明細があったが、主要値のみを取り込んでいた。按分による推定値を作り、明細の提供を求める確認事項を起票していた</t>
+          <t>98本中97本。別ブランチの作業ツリーから実行すると生成物がそこへ落ちる。実際に起きた</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>明細を `data_nenpo_meisai.py` に収め、推定値を確定値に置き換えた。確認事項No.134は当方の取込漏れによるものとして取り下げた。確認事項を起こす前に受領済みのファイルを確かめる</t>
+          <t>`repo_paths.py` を新設し `RP.ROOT`（`__file__` 起点）に統一した。全スクリプトを別ディレクトリから実行して確認した</t>
         </is>
       </c>
     </row>
@@ -2993,22 +2993,22 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>「差し替えは4画面ある」と確かめずに断定した</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>R8.9.12</t>
+          <t>受領済みの年報の明細を取り込まないまま推定値を作っていた</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R8.9.11</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるかを確かめていなかった。受領した画面の写しには写っていない</t>
+          <t>年報（令和7年度・資料No.22）に要介護度別の明細があったが、主要値のみを取り込んでいた。按分による推定値を作り、明細の提供を求める確認事項を起票していた</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>「編集項目の有無を要確認」に改め、確認事項No.138として起票した。画面で確かめていないことは断定しない</t>
+          <t>明細を `data_nenpo_meisai.py` に収め、推定値を確定値に置き換えた。確認事項No.134は当方の取込漏れによるものとして取り下げた。確認事項を起こす前に受領済みのファイルを確かめる</t>
         </is>
       </c>
     </row>
@@ -3018,22 +3018,22 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の集計値を暫定のまま置きかけた</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>R8.9.15</t>
+          <t>「差し替えは4画面ある」と確かめずに断定した</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>R8.9.12</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>社会参加・暮らし向きの値を仮に置いたまま素案へ渡そうとした。出所との突合で気付いた</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるかを確かめていなかった。受領した画面の写しには写っていない</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>全項目を機械的に突合して実際の値に直した（不一致0）。データモジュールを作ったら出所と全項目を突き合わせる</t>
+          <t>「編集項目の有無を要確認」に改め、確認事項No.138として起票した。画面で確かめていないことは断定しない</t>
         </is>
       </c>
     </row>
@@ -3043,30 +3043,55 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
+          <t>健康とくらしの調査の集計値を暫定のまま置きかけた</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>R8.9.15</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>社会参加・暮らし向きの値を仮に置いたまま素案へ渡そうとした。出所との突合で気付いた</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>全項目を機械的に突合して実際の値に直した（不一致0）。データモジュールを作ったら出所と全項目を突き合わせる</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
           <t>認定率の差を「分子に第2号被保険者を含むかの違い」としていた</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>R8.9.16</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>確認事項No.125の起票時の見立て。受領資料を数値で確かめないまま原因を1つに決めていた。令和8年9月16日に逆算して確かめたところ、当方の認定率は分子に第2号被保険者の認定者を含んでおらず、見える化システムの総括表にも要介護認定率の行があって1,943÷9,119で小数第6位まで再現できることが分かった</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.125を「将来推計の参考シートの認定率が総括表の認定率と一致しないこと」に絞って書き直した。**差の原因を1つに決める前に、受領資料の数値で逆算して確かめる**</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>注1）11件のうち算定に関わるものが5件、記述が5件、運用が1件です。
-注2）算定に関わる5件のうち、保険料の算定に影響したのは調整交付金の表示（49,113円）のみで、他は表示・推定値の置き方・定員の集計に関わるものです。
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.125を「将来推計の参考シートの認定率が総括表の認定率と一致しないこと」に絞って書き直した。差の原因を1つに決める前に、受領資料の数値で逆算して確かめる</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>注1）12件のうち算定に関わるものが6件、記述が5件、運用が1件です。
+注2）算定に関わる6件のうち、保険料の算定に影響したのは調整交付金の表示（49,113円）のみで、他は表示・推定値の置き方・定員の集計に関わるものです。
 注3）当方の自己点検が見つけたもの4件、ブランチ内資料の点検によるご指摘3件、受領資料の再送により判明したもの1件です。
 注4）いずれも「手立て」の欄に記した内容をCLAUDE.mdの「陥りやすい誤り」に記録し、同じ誤りを繰り返さない形にしています。</t>
         </is>
@@ -3075,8 +3100,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3157,7 +3182,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>114本（うち再実行できない3本）</t>
+          <t>115本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3386,7 +3411,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>11件</t>
+          <t>12件</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -3443,7 +3468,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>115件＝送付34＋条件付き53＋内部保管23＋対象外5</t>
+          <t>116件＝送付34＋条件付き54＋内部保管23＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は926段落145表36図です。</t>
+注3）計画素案は928段落145表36図です。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／115本</t>
+          <t>3／116本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の112本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の113本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全115本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全116本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>112／115本が可能</t>
+          <t>113／116本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は116件（送付34・条件付き54・内部保管23・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は117件（送付34・条件付き55・内部保管23・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>115本（うち再実行できない3本）</t>
+          <t>116本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>116件＝送付34＋条件付き54＋内部保管23＋対象外5</t>
+          <t>117件＝送付34＋条件付き55＋内部保管23＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／116本</t>
+          <t>3／117本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の113本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の114本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表158件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表167件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全116本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全117本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>113／116本が可能</t>
+          <t>114／117本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（158件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（167件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜158</t>
+          <t>No.1〜167</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>158件</t>
+          <t>167件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は117件（送付34・条件付き55・内部保管23・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は118件（送付35・条件付き55・内部保管23・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>116本（うち再実行できない3本）</t>
+          <t>117本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>158件／一意158件</t>
+          <t>167件／一意167件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>117件＝送付34＋条件付き55＋内部保管23＋対象外5</t>
+          <t>118件＝送付35＋条件付き55＋内部保管23＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／117本</t>
+          <t>3／118本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の114本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の115本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全117本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全118本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>114／117本が可能</t>
+          <t>115／118本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は118件（送付35・条件付き55・内部保管23・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は120件（送付37・条件付き55・内部保管23・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>117本（うち再実行できない3本）</t>
+          <t>118本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>118件＝送付35＋条件付き55＋内部保管23＋対象外5</t>
+          <t>120件＝送付37＋条件付き55＋内部保管23＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／118本</t>
+          <t>3／119本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の115本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の116本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表167件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表169件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全118本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全119本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>115／118本が可能</t>
+          <t>116／119本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（167件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（169件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜167</t>
+          <t>No.1〜169</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>167件</t>
+          <t>169件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は120件（送付37・条件付き55・内部保管23・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は122件（送付39・条件付き55・内部保管23・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>118本（うち再実行できない3本）</t>
+          <t>119本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>167件／一意167件</t>
+          <t>169件／一意169件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>120件＝送付37＋条件付き55＋内部保管23＋対象外5</t>
+          <t>122件＝送付39＋条件付き55＋内部保管23＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／119本</t>
+          <t>3／120本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の116本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の117本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表169件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表171件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は928段落145表36図です。</t>
+注3）計画素案は943段落147表36図です。</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全119本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全120本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>116／119本が可能</t>
+          <t>117／120本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（169件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（171件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜169</t>
+          <t>No.1〜171</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>169件</t>
+          <t>171件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は122件（送付39・条件付き55・内部保管23・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は123件（送付40・条件付き55・内部保管23・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>119本（うち再実行できない3本）</t>
+          <t>120本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>169件／一意169件</t>
+          <t>171件／一意171件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>122件＝送付39＋条件付き55＋内部保管23＋対象外5</t>
+          <t>123件＝送付40＋条件付き55＋内部保管23＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は943段落147表36図です。</t>
+注3）計画素案は916段落141表36図です。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は916段落141表36図です。</t>
+注3）計画素案は927段落143表36図です。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／120本</t>
+          <t>3／122本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の117本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の119本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は927段落143表36図です。</t>
+注3）計画素案は928段落143表36図です。</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全120本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全122本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>117／120本が可能</t>
+          <t>119／122本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は123件（送付40・条件付き55・内部保管23・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は124件（送付41・条件付き55・内部保管23・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>120本（うち再実行できない3本）</t>
+          <t>122本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>123件＝送付40＋条件付き55＋内部保管23＋対象外5</t>
+          <t>124件＝送付41＋条件付き55＋内部保管23＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／122本</t>
+          <t>3／123本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の119本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の120本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表171件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表173件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全122本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全123本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>119／122本が可能</t>
+          <t>120／123本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（171件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（173件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜171</t>
+          <t>No.1〜173</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>171件</t>
+          <t>173件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は124件（送付41・条件付き55・内部保管23・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は125件（送付41・条件付き55・内部保管24・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>122本（うち再実行できない3本）</t>
+          <t>123本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>171件／一意171件</t>
+          <t>173件／一意173件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>124件＝送付41＋条件付き55＋内部保管23＋対象外5</t>
+          <t>125件＝送付41＋条件付き55＋内部保管24＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／123本</t>
+          <t>3／126本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の120本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の123本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全123本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全126本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>120／123本が可能</t>
+          <t>123／126本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は125件（送付41・条件付き55・内部保管24・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は128件（送付43・条件付き56・内部保管24・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>123本（うち再実行できない3本）</t>
+          <t>126本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>125件＝送付41＋条件付き55＋内部保管24＋対象外5</t>
+          <t>128件＝送付43＋条件付き56＋内部保管24＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／126本</t>
+          <t>3／127本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の123本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の124本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全126本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全127本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>123／126本が可能</t>
+          <t>124／127本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は128件（送付43・条件付き56・内部保管24・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は129件（送付43・条件付き56・内部保管25・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>126本（うち再実行できない3本）</t>
+          <t>127本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>128件＝送付43＋条件付き56＋内部保管24＋対象外5</t>
+          <t>129件＝送付43＋条件付き56＋内部保管25＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／127本</t>
+          <t>3／128本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の124本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の125本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は928段落143表36図です。</t>
+注3）計画素案は942段落145表36図です。</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全127本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全128本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>124／127本が可能</t>
+          <t>125／128本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は129件（送付43・条件付き56・内部保管25・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は130件（送付44・条件付き56・内部保管25・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>127本（うち再実行できない3本）</t>
+          <t>128本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>129件＝送付43＋条件付き56＋内部保管25＋対象外5</t>
+          <t>130件＝送付44＋条件付き56＋内部保管25＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は942段落145表36図です。</t>
+注3）計画素案は949段落146表36図です。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は949段落146表36図です。</t>
+注3）計画素案は951段落146表36図です。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／128本</t>
+          <t>3／129本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の125本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の126本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全128本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全129本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>125／128本が可能</t>
+          <t>126／129本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は130件（送付44・条件付き56・内部保管25・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は132件（送付44・条件付き58・内部保管25・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>128本（うち再実行できない3本）</t>
+          <t>129本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>130件＝送付44＋条件付き56＋内部保管25＋対象外5</t>
+          <t>132件＝送付44＋条件付き58＋内部保管25＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -3635,7 +3635,7 @@
       <c r="D6" s="6" t="inlineStr">
         <is>
           <t>町別データシート
-サービス見込量 第1次概算</t>
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／129本</t>
+          <t>3／130本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の126本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の127本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全129本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全130本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>126／129本が可能</t>
+          <t>127／130本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は132件（送付44・条件付き58・内部保管25・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は133件（送付45・条件付き58・内部保管25・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>129本（うち再実行できない3本）</t>
+          <t>130本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>132件＝送付44＋条件付き58＋内部保管25＋対象外5</t>
+          <t>133件＝送付45＋条件付き58＋内部保管25＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -2740,7 +2740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2793,22 +2793,22 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の給付費の差を抽出条件の違いによるものと整理していた</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>R8.9.25</t>
+          <t>公表版に取り込んでいる図2点が是正前のものであった</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>R8.10.4</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領分の【大雪】令和7年度のファイルの表の値3,083,474,291円を広域連合の実績として扱い、「町別に按分すると3町とも上回る」「広域連合のファイルだけ伸びが趨勢から外れている」と整理していた。同じファイルの明細を集計すると3町合計と要介護度別まで一致する</t>
+          <t>令和8年9月29日に美瑛町のスクールバス（宇莫別線 6,268→6,165人）と保険料の要因分解の累計4か所を是正したが、協議用素案の側だけが是正後になっており、公表版は是正前の図を取り込んだままであった。全ての処理を名の順に一度通すと、計画素案が作図より先に走るため収束しない</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>再提供を受けたファイルにより差が解消したことを確かめ、従前の整理を取り下げた。表（ピボット）の値は、同じファイルの明細と突き合わせてから用いる</t>
+          <t>作図→計画素案→公表版の順に実行し直し、公表版の図を差し替えた。別の場所に複製した状態で作り直した成果品と中身を突き合わせる点検を設け、収束していないものが出るようにした</t>
         </is>
       </c>
     </row>
@@ -2818,22 +2818,22 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の割合を7.375％と表示していた</t>
+          <t>令和7年度の給付費の差を抽出条件の違いによるものと整理していた</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>R8.9.11</t>
+          <t>R8.9.25</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>実際の計算は7.3755％で、Eの算定で49,113円の差。ブランチ内資料の点検によるご指摘</t>
+          <t>令和8年8月28日受領分の【大雪】令和7年度のファイルの表の値3,083,474,291円を広域連合の実績として扱い、「町別に按分すると3町とも上回る」「広域連合のファイルだけ伸びが趨勢から外れている」と整理していた。同じファイルの明細を集計すると3町合計と要介護度別まで一致する</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>表示を7.3755％に改めた。表示の桁を落とさず、計算に用いた値をそのまま書く</t>
+          <t>再提供を受けたファイルにより差が解消したことを確かめ、従前の整理を取り下げた。表（ピボット）の値は、同じファイルの明細と突き合わせてから用いる</t>
         </is>
       </c>
     </row>
@@ -2843,22 +2843,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>`data_shien_tool.SHISETSU` を「定員」と表記していた</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>R8.9.10</t>
+          <t>調整交付金の割合を7.375％と表示していた</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>R8.9.11</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>実際は月平均利用者数。町別データシートの表題が誤っていた</t>
+          <t>実際の計算は7.3755％で、Eの算定で49,113円の差。ブランチ内資料の点検によるご指摘</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>「施設・居住系サービスの月平均利用者数」に改めた。定員と読み違えやすい値4つをCLAUDE.mdに記録した</t>
+          <t>表示を7.3755％に改めた。表示の桁を落とさず、計算に用いた値をそのまま書く</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>令和9年度が介護報酬改定の年に当たらないとしていた</t>
+          <t>`data_shien_tool.SHISETSU` を「定員」と表記していた</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>改定は3年周期（H30・R3・R6）であり令和9年度は改定の年。`build_machi_kaito.py` の記述</t>
+          <t>実際は月平均利用者数。町別データシートの表題が誤っていた</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>修正した。改定率1％あたり月額＋61円を算定し、確認事項No.109として起票した</t>
+          <t>「施設・居住系サービスの月平均利用者数」に改めた。定員と読み違えやすい値4つをCLAUDE.mdに記録した</t>
         </is>
       </c>
     </row>
@@ -2893,22 +2893,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>「2か年とも基本推計が実績に近い」としていた</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>R8.9.11</t>
+          <t>令和9年度が介護報酬改定の年に当たらないとしていた</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>R8.9.10</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>令和6年度は包括推計の方が1.00に近い。自己点検が検出した</t>
+          <t>改定は3年周期（H30・R3・R6）であり令和9年度は改定の年。`build_machi_kaito.py` の記述</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2か年平均の絶対誤差（基本0.61％・包括1.23％）で比べる形に改めた。「2か年とも」と書く前に各年を確かめる</t>
+          <t>修正した。改定率1％あたり月額＋61円を算定し、確認事項No.109として起票した</t>
         </is>
       </c>
     </row>
@@ -2918,22 +2918,22 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の町別定員が誤っていた</t>
+          <t>「2か年とも基本推計が実績に近い」としていた</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>R8.9.10</t>
+          <t>R8.9.11</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>東川町45人→36人、計108人→99人。第2章第3節6及び第6章第4節4の分布欄</t>
+          <t>令和6年度は包括推計の方が1.00に近い。自己点検が検出した</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>修正した。定員は99人＋［要確認］とし、くるみの郷の定員未確定を明示している</t>
+          <t>2か年平均の絶対誤差（基本0.61％・包括1.23％）で比べる形に改めた。「2か年とも」と書く前に各年を確かめる</t>
         </is>
       </c>
     </row>
@@ -2943,22 +2943,22 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>素案の段落・表・図の数が管理表と合っていなかった</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>R8.9.11</t>
+          <t>認知症対応型共同生活介護の町別定員が誤っていた</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>R8.9.10</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>実物806／130／36に対し管理表667／114／34。固定値で書いていたため更新に追随していなかった</t>
+          <t>東川町45人→36人、計108人→99人。第2章第3節6及び第6章第4節4の分布欄</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>`repo_paths.draft_label()` で実物から数える形に改め、6箇所を置換した。件数・項目数は固定値で書かない</t>
+          <t>修正した。定員は99人＋［要確認］とし、くるみの郷の定員未確定を明示している</t>
         </is>
       </c>
     </row>
@@ -2968,22 +2968,22 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>ビルドスクリプトが出力先を絶対パスで固定していた</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
+          <t>素案の段落・表・図の数が管理表と合っていなかった</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>R8.9.11</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>98本中97本。別ブランチの作業ツリーから実行すると生成物がそこへ落ちる。実際に起きた</t>
+          <t>実物806／130／36に対し管理表667／114／34。固定値で書いていたため更新に追随していなかった</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>`repo_paths.py` を新設し `RP.ROOT`（`__file__` 起点）に統一した。全スクリプトを別ディレクトリから実行して確認した</t>
+          <t>`repo_paths.draft_label()` で実物から数える形に改め、6箇所を置換した。件数・項目数は固定値で書かない</t>
         </is>
       </c>
     </row>
@@ -2993,22 +2993,22 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>受領済みの年報の明細を取り込まないまま推定値を作っていた</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
+          <t>ビルドスクリプトが出力先を絶対パスで固定していた</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>R8.9.11</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>年報（令和7年度・資料No.22）に要介護度別の明細があったが、主要値のみを取り込んでいた。按分による推定値を作り、明細の提供を求める確認事項を起票していた</t>
+          <t>98本中97本。別ブランチの作業ツリーから実行すると生成物がそこへ落ちる。実際に起きた</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>明細を `data_nenpo_meisai.py` に収め、推定値を確定値に置き換えた。確認事項No.134は当方の取込漏れによるものとして取り下げた。確認事項を起こす前に受領済みのファイルを確かめる</t>
+          <t>`repo_paths.py` を新設し `RP.ROOT`（`__file__` 起点）に統一した。全スクリプトを別ディレクトリから実行して確認した</t>
         </is>
       </c>
     </row>
@@ -3018,22 +3018,22 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>「差し替えは4画面ある」と確かめずに断定した</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>R8.9.12</t>
+          <t>受領済みの年報の明細を取り込まないまま推定値を作っていた</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R8.9.11</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるかを確かめていなかった。受領した画面の写しには写っていない</t>
+          <t>年報（令和7年度・資料No.22）に要介護度別の明細があったが、主要値のみを取り込んでいた。按分による推定値を作り、明細の提供を求める確認事項を起票していた</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>「編集項目の有無を要確認」に改め、確認事項No.138として起票した。画面で確かめていないことは断定しない</t>
+          <t>明細を `data_nenpo_meisai.py` に収め、推定値を確定値に置き換えた。確認事項No.134は当方の取込漏れによるものとして取り下げた。確認事項を起こす前に受領済みのファイルを確かめる</t>
         </is>
       </c>
     </row>
@@ -3043,22 +3043,22 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の集計値を暫定のまま置きかけた</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>R8.9.15</t>
+          <t>「差し替えは4画面ある」と確かめずに断定した</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>R8.9.12</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>社会参加・暮らし向きの値を仮に置いたまま素案へ渡そうとした。出所との突合で気付いた</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるかを確かめていなかった。受領した画面の写しには写っていない</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>全項目を機械的に突合して実際の値に直した（不一致0）。データモジュールを作ったら出所と全項目を突き合わせる</t>
+          <t>「編集項目の有無を要確認」に改め、確認事項No.138として起票した。画面で確かめていないことは断定しない</t>
         </is>
       </c>
     </row>
@@ -3068,29 +3068,54 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
+          <t>健康とくらしの調査の集計値を暫定のまま置きかけた</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>R8.9.15</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>社会参加・暮らし向きの値を仮に置いたまま素案へ渡そうとした。出所との突合で気付いた</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>全項目を機械的に突合して実際の値に直した（不一致0）。データモジュールを作ったら出所と全項目を突き合わせる</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="50" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
           <t>認定率の差を「分子に第2号被保険者を含むかの違い」としていた</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>R8.9.16</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>確認事項No.125の起票時の見立て。受領資料を数値で確かめないまま原因を1つに決めていた。令和8年9月16日に逆算して確かめたところ、当方の認定率は分子に第2号被保険者の認定者を含んでおらず、見える化システムの総括表にも要介護認定率の行があって1,943÷9,119で小数第6位まで再現できることが分かった</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>確認事項No.125を「将来推計の参考シートの認定率が総括表の認定率と一致しないこと」に絞って書き直した。差の原因を1つに決める前に、受領資料の数値で逆算して確かめる</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>注1）12件のうち算定に関わるものが6件、記述が5件、運用が1件です。
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>注1）13件のうち算定に関わるものが6件、記述が6件、運用が1件です。
 注2）算定に関わる6件のうち、保険料の算定に影響したのは調整交付金の表示（49,113円）のみで、他は表示・推定値の置き方・定員の集計に関わるものです。
 注3）当方の自己点検が見つけたもの4件、ブランチ内資料の点検によるご指摘3件、受領資料の再送により判明したもの1件です。
 注4）いずれも「手立て」の欄に記した内容をCLAUDE.mdの「陥りやすい誤り」に記録し、同じ誤りを繰り返さない形にしています。</t>
@@ -3101,7 +3126,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A19:E19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3411,7 +3436,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>12件</t>
+          <t>13件</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は951段落146表36図です。</t>
+注3）計画素案は973段落148表36図です。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／130本</t>
+          <t>3／131本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の127本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の128本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全130本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全131本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>127／130本が可能</t>
+          <t>128／131本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は133件（送付45・条件付き58・内部保管25・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は134件（送付45・条件付き58・内部保管26・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>130本（うち再実行できない3本）</t>
+          <t>131本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>133件＝送付45＋条件付き58＋内部保管25＋対象外5</t>
+          <t>134件＝送付45＋条件付き58＋内部保管26＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表173件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表174件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（173件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（174件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜173</t>
+          <t>No.1〜174</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>173件</t>
+          <t>174件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>173件／一意173件</t>
+          <t>174件／一意174件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／131本</t>
+          <t>3／132本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の128本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の129本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全131本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全132本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>128／131本が可能</t>
+          <t>129／132本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は134件（送付45・条件付き58・内部保管26・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は135件（送付46・条件付き58・内部保管26・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>131本（うち再実行できない3本）</t>
+          <t>132本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>134件＝送付45＋条件付き58＋内部保管26＋対象外5</t>
+          <t>135件＝送付46＋条件付き58＋内部保管26＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表174件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表177件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は973段落148表36図です。</t>
+注3）計画素案は1000段落151表36図です。</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（174件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（177件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜174</t>
+          <t>No.1〜177</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>174件</t>
+          <t>177件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>174件／一意174件</t>
+          <t>177件／一意177件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は1000段落151表36図です。</t>
+注3）計画素案は1001段落151表36図です。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表177件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表181件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は1001段落151表36図です。</t>
+注3）計画素案は1024段落152表36図です。</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（177件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（181件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜177</t>
+          <t>No.1〜181</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>177件</t>
+          <t>181件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>177件／一意177件</t>
+          <t>181件／一意181件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／132本</t>
+          <t>3／133本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の129本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の130本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表181件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表184件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は1024段落152表36図です。</t>
+注3）計画素案は1027段落153表36図です。</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全132本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全133本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>129／132本が可能</t>
+          <t>130／133本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（181件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（184件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜181</t>
+          <t>No.1〜184</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>181件</t>
+          <t>184件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は135件（送付46・条件付き58・内部保管26・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は136件（送付47・条件付き58・内部保管26・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>132本（うち再実行できない3本）</t>
+          <t>133本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>181件／一意181件</t>
+          <t>184件／一意184件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>135件＝送付46＋条件付き58＋内部保管26＋対象外5</t>
+          <t>136件＝送付47＋条件付き58＋内部保管26＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／133本</t>
+          <t>3／134本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の130本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の131本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は1027段落153表36図です。</t>
+注3）計画素案は1030段落153表36図です。</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全133本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全134本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>130／133本が可能</t>
+          <t>131／134本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は136件（送付47・条件付き58・内部保管26・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は137件（送付48・条件付き58・内部保管26・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>133本（うち再実行できない3本）</t>
+          <t>134本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>136件＝送付47＋条件付き58＋内部保管26＋対象外5</t>
+          <t>137件＝送付48＋条件付き58＋内部保管26＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は1030段落153表36図です。</t>
+注3）計画素案は1038段落153表36図です。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／134本</t>
+          <t>3／135本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の131本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の132本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表184件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表186件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は1038段落153表36図です。</t>
+注3）計画素案は1060段落156表36図です。</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全134本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全135本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>131／134本が可能</t>
+          <t>132／135本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（184件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（186件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜184</t>
+          <t>No.1〜186</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>184件</t>
+          <t>186件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は137件（送付48・条件付き58・内部保管26・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は138件（送付49・条件付き58・内部保管26・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>134本（うち再実行できない3本）</t>
+          <t>135本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>184件／一意184件</t>
+          <t>186件／一意186件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>137件＝送付48＋条件付き58＋内部保管26＋対象外5</t>
+          <t>138件＝送付49＋条件付き58＋内部保管26＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／135本</t>
+          <t>3／136本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の132本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の133本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は1060段落156表36図です。</t>
+注3）計画素案は1059段落156表36図です。</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全135本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全136本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>132／135本が可能</t>
+          <t>133／136本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は138件（送付49・条件付き58・内部保管26・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は139件（送付50・条件付き58・内部保管26・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>135本（うち再実行できない3本）</t>
+          <t>136本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>138件＝送付49＋条件付き58＋内部保管26＋対象外5</t>
+          <t>139件＝送付50＋条件付き58＋内部保管26＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／136本</t>
+          <t>3／138本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の133本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の135本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表186件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表189件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は1059段落156表36図です。</t>
+注3）計画素案は1062段落156表36図です。</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全136本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全138本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>133／136本が可能</t>
+          <t>135／138本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（186件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（189件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜186</t>
+          <t>No.1〜189</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>186件</t>
+          <t>189件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は139件（送付50・条件付き58・内部保管26・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は141件（送付52・条件付き58・内部保管26・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>136本（うち再実行できない3本）</t>
+          <t>138本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>186件／一意186件</t>
+          <t>189件／一意189件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>139件＝送付50＋条件付き58＋内部保管26＋対象外5</t>
+          <t>141件＝送付52＋条件付き58＋内部保管26＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／138本</t>
+          <t>3／139本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の135本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の136本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全138本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全139本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>135／138本が可能</t>
+          <t>136／139本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は141件（送付52・条件付き58・内部保管26・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は142件（送付52・条件付き59・内部保管26・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>138本（うち再実行できない3本）</t>
+          <t>139本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>141件＝送付52＋条件付き58＋内部保管26＋対象外5</t>
+          <t>142件＝送付52＋条件付き59＋内部保管26＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／139本</t>
+          <t>3／140本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の136本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の137本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表189件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表190件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は1062段落156表36図です。</t>
+注3）計画素案は1063段落156表36図です。</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全139本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全140本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>136／139本が可能</t>
+          <t>137／140本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（189件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（190件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜189</t>
+          <t>No.1〜190</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>189件</t>
+          <t>190件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は142件（送付52・条件付き59・内部保管26・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は143件（送付53・条件付き59・内部保管26・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>139本（うち再実行できない3本）</t>
+          <t>140本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>189件／一意189件</t>
+          <t>190件／一意190件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>142件＝送付52＋条件付き59＋内部保管26＋対象外5</t>
+          <t>143件＝送付53＋条件付き59＋内部保管26＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／140本</t>
+          <t>3／141本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の137本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の138本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は1063段落156表36図です。</t>
+注3）計画素案は1074段落158表36図です。</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全140本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全141本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>137／140本が可能</t>
+          <t>138／141本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は143件（送付53・条件付き59・内部保管26・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は144件（送付54・条件付き59・内部保管26・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>140本（うち再実行できない3本）</t>
+          <t>141本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>143件＝送付53＋条件付き59＋内部保管26＋対象外5</t>
+          <t>144件＝送付54＋条件付き59＋内部保管26＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／141本</t>
+          <t>3／142本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の138本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の139本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表190件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表192件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全141本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全142本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>138／141本が可能</t>
+          <t>139／142本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（190件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（192件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜190</t>
+          <t>No.1〜192</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>190件</t>
+          <t>192件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は144件（送付54・条件付き59・内部保管26・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は145件（送付55・条件付き59・内部保管26・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>141本（うち再実行できない3本）</t>
+          <t>142本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>190件／一意190件</t>
+          <t>192件／一意192件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>144件＝送付54＋条件付き59＋内部保管26＋対象外5</t>
+          <t>145件＝送付55＋条件付き59＋内部保管26＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">

--- a/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
+++ b/output/第10期計画_管理の統合と成果品の棚卸し.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3／142本</t>
+          <t>3／144本</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>いずれも受領資料をセッション固有の場所から読むもの。他の139本は再実行できる（01シート）</t>
+          <t>いずれも受領資料をセッション固有の場所から読むもの。他の141本は再実行できる（01シート）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表192件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
+          <t>業務工程管理表193件と計画素案の別管理表60件（A25・B35）。番号体系が別で、同じ問いを二重に管理しているものが8件ある（02シート）</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
         <is>
           <t>注1）本表は成果品を減らすことそのものを目的とはしていません。どれが現に用いられ、どれが役割を終えたかを示し、納品時の構成をご判断いただくための材料とするものです。
 注2）誤りを正した記録は、当方の作業の信頼性を確かめていただくために残すものです。内部保管とせず送付資料に含めています。
-注3）計画素案は1074段落158表36図です。</t>
+注3）計画素案は1090段落161表36図です。</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全142本のビルドスクリプトを実行している。</t>
+          <t>発注者のご判断を待たずに当方の側で確かめられることを点検した。令和8年9月15日に全144本のビルドスクリプトを実行している。</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>139／142本が可能</t>
+          <t>141／144本が可能</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧（192件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧（193件）と計画素案の別管理表 03・04シート（A25件・B35件）の2か所にあり、番号体系も別である。同じ問いを二重に管理しているものを示す。</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>No.1〜192</t>
+          <t>No.1〜193</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>192件</t>
+          <t>193件</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2720,7 +2720,7 @@
           <t>注1）13件のうち、統合済みが4件・会議終了が7件です。
 注2）統合済みの4件は統合報告書（44シート）に収録済みで内容は同一です。元の4件を残すか、統合報告書に一本化するかはご判断をお願いします（確認事項No.144）。残す場合、同じ内容が2か所にあることになります。
 注3）会議終了の6件は内部保管であり、送付資料には含めていません。納品時は「その他業務で作成した資料 一式」に含めます。統合候補の群6に当たり、1件へ束ねることができます。
-注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は145件（送付55・条件付き59・内部保管26・対象外5）です。</t>
+注4）本シートは削除を提案するものではありません。作業の記録は納品まで残します。現在の成果品は146件（送付56・条件付き59・内部保管26・対象外5）です。</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>142本（うち再実行できない3本）</t>
+          <t>144本（うち再実行できない3本）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>192件／一意192件</t>
+          <t>193件／一意193件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>145件＝送付55＋条件付き59＋内部保管26＋対象外5</t>
+          <t>146件＝送付56＋条件付き59＋内部保管26＋対象外5</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
